--- a/data/CdS1/CdS1_IV Graph.xlsx
+++ b/data/CdS1/CdS1_IV Graph.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{A9C2BFFF-8191-40CA-A12D-E3F85024474C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{94680694-794B-483A-A68D-DA1904E50ABA}"/>
+    <workbookView xWindow="3924" yWindow="6024" windowWidth="17280" windowHeight="8880" xr2:uid="{94680694-794B-483A-A68D-DA1904E50ABA}"/>
   </bookViews>
   <sheets>
     <sheet name="CdS1_IV Graph_1" sheetId="1" r:id="rId1"/>
